--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -73,10 +73,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
+    <t>ORTIZ</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -85,12 +82,6 @@
     <t>PIÑA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -109,21 +100,12 @@
     <t>TORRES</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GIL</t>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>GUZMAN</t>
   </si>
   <si>
@@ -139,22 +121,13 @@
     <t>SALAS</t>
   </si>
   <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JESUS</t>
+    <t>BARUCH BOSET</t>
   </si>
   <si>
     <t>KARINA</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
   </si>
   <si>
     <t>KARENT LILIANA</t>
@@ -622,7 +595,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -631,10 +604,10 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>78.38</v>
+        <v>78.95</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -648,7 +621,7 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -657,10 +630,10 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
@@ -716,16 +689,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -739,16 +715,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -759,13 +738,13 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -782,13 +761,13 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -850,16 +829,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>92.86</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -876,16 +855,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>80.95</v>
+        <v>92.86</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -896,7 +875,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -905,10 +884,10 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>78.38</v>
+        <v>78.95</v>
       </c>
       <c r="H4">
         <v>7.1</v>
@@ -922,7 +901,7 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -931,10 +910,10 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
@@ -947,7 +926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -979,16 +958,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920116</v>
+        <v>22330051920108</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1002,22 +981,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920122</v>
+        <v>22330051920133</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1028,16 +1007,16 @@
         <v>22330051920133</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -1048,19 +1027,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920133</v>
+        <v>22330051920352</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -1071,16 +1050,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920352</v>
+        <v>22330051920128</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1089,27 +1068,27 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920088</v>
+        <v>22330051920248</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1117,22 +1096,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920121</v>
+        <v>22330061460548</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1140,16 +1119,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920128</v>
+        <v>22330051920110</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1163,19 +1142,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920248</v>
+        <v>22330051920354</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -1186,16 +1165,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330061460548</v>
+        <v>22330051920145</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1204,75 +1183,6 @@
         <v>11</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920110</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920354</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920145</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -76,7 +76,10 @@
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>PIÑA</t>
@@ -85,46 +88,46 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
     <t>BARUCH BOSET</t>
   </si>
   <si>
-    <t>KARINA</t>
+    <t>ABIGAIL ANTONIA</t>
+  </si>
+  <si>
+    <t>ZURI GABRIELA</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -133,19 +136,13 @@
     <t>KARENT LILIANA</t>
   </si>
   <si>
-    <t>JOSE ALBIN</t>
-  </si>
-  <si>
-    <t>NORMA ANGELICA</t>
+    <t>LUISA MARIA</t>
   </si>
   <si>
     <t>ODALIS SOFIA</t>
   </si>
   <si>
     <t>KEVIN</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
   </si>
 </sst>
 </file>
@@ -741,16 +738,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.58</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -764,16 +764,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>81.58</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -881,16 +884,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>78.95</v>
+        <v>81.58</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -907,16 +910,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>92.11</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -964,7 +967,7 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -981,13 +984,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920133</v>
+        <v>22330051920130</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
@@ -1004,13 +1007,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920133</v>
+        <v>22330051920130</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
         <v>35</v>
@@ -1027,7 +1030,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920352</v>
+        <v>22330051920138</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -1050,39 +1053,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920128</v>
+        <v>22330051920138</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920248</v>
+        <v>22330051920352</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1091,21 +1094,21 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330061460548</v>
+        <v>22330051920128</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1119,19 +1122,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920110</v>
+        <v>22330051920246</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -1142,19 +1145,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920354</v>
+        <v>22330051920110</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -1165,19 +1168,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920145</v>
+        <v>22330051920354</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
@@ -738,7 +738,7 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -750,7 +750,7 @@
         <v>81.58</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -764,16 +764,16 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>81.58</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -73,76 +73,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ORTIZ</t>
+    <t>MENDOZA</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>PIÑA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>OJEDA</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>BARUCH BOSET</t>
+    <t>VALERIA</t>
   </si>
   <si>
     <t>ABIGAIL ANTONIA</t>
   </si>
   <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
     <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>KARENT LILIANA</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>ODALIS SOFIA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
   </si>
 </sst>
 </file>
@@ -832,16 +787,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -858,16 +813,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>92.86</v>
+        <v>97.62</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -884,16 +839,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>81.58</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -910,13 +865,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>84.20999999999999</v>
+        <v>92.11</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -929,7 +884,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -961,16 +916,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920108</v>
+        <v>22330051920105</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -990,202 +945,41 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920130</v>
+        <v>22330051920352</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920138</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920138</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920352</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920128</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920246</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920110</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920354</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
@@ -796,7 +796,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -822,7 +822,7 @@
         <v>97.62</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -848,7 +848,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -874,7 +874,7 @@
         <v>92.11</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20231.xlsx
@@ -796,7 +796,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -822,7 +822,7 @@
         <v>97.62</v>
       </c>
       <c r="H3">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -848,7 +848,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H4">
-        <v>9.699999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -874,7 +874,7 @@
         <v>92.11</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
